--- a/AI_Skill/OtherSkills/OtherSkills.xlsx
+++ b/AI_Skill/OtherSkills/OtherSkills.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第三方技能清单" sheetId="1" r:id="R59d2c2a7b5be4fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第三方技能清单" sheetId="1" r:id="Radb5fe4cc9cb4d17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -115,7 +115,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -189,6 +189,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -198,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OtherSkillsTable" displayName="OtherSkillsTable" ref="A4:J5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:J5"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OtherSkillsTable" displayName="OtherSkillsTable" ref="A4:J6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:J6"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="技能名称"/>
     <x:tableColumn id="2" name="发布者"/>
@@ -442,15 +448,15 @@
         <x:v>技能数量</x:v>
       </x:c>
       <x:c r="B2" s="13" t="n">
-        <x:f>COUNTA(A5:A200)</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTA(A5:A6)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="10"/>
       <x:c r="D2" s="12" t="str">
         <x:v>清单日期</x:v>
       </x:c>
       <x:c r="E2" s="11" t="n">
-        <x:v>46263</x:v>
+        <x:v>46268</x:v>
       </x:c>
       <x:c r="F2" s="10"/>
       <x:c r="G2" s="10" t="str">
@@ -522,6 +528,40 @@
       </x:c>
       <x:c r="J5" s="30" t="str">
         <x:v>其他环境应根据官方仓库地址重新下载，不从本仓库获取源码。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="120" customHeight="1">
+      <x:c r="A6" s="35" t="str">
+        <x:v>cordis-plugin-development</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="str">
+        <x:v>DeepSeek</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="str">
+        <x:v>开发 Cordis 会话内动态插件；已合入 dsh-plugin-creator，仅作官方来源参考。</x:v>
+      </x:c>
+      <x:c r="D6" s="35" t="str">
+        <x:v>https://github.com/deepseek-ai/deepseek-harness</x:v>
+      </x:c>
+      <x:c r="E6" s="35" t="str">
+        <x:v>https://github.com/deepseek-ai/deepseek-harness</x:v>
+      </x:c>
+      <x:c r="F6" s="35" t="str">
+        <x:v>MIT</x:v>
+      </x:c>
+      <x:c r="G6" s="35" t="str">
+        <x:v>49a606bc</x:v>
+      </x:c>
+      <x:c r="H6" s="35" t="str">
+        <x:v>不单独安装</x:v>
+      </x:c>
+      <x:c r="I6" s="35" t="str">
+        <x:v>已下载官方原文与许可证</x:v>
+      </x:c>
+      <x:c r="J6" s="35" t="str">
+        <x:v>来源路径：packages/preset/agent-presets/presets/cordis/skills/cordis-plugin-development/SKILL.md
+提交：49a606bc5b5934603f22a26957a07dc799ab0291
+下载日期：2026-09-03；仅作来源参考。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -531,7 +571,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re24823d18f3d48ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc022d2f36ab74818"/>
   </x:tableParts>
 </x:worksheet>
 </file>